--- a/research/traditional_assets/database/data/israel/israel_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_financial_svcs_non_bank_insurance.xlsx
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.142</v>
+        <v>0.16</v>
       </c>
       <c r="E2">
-        <v>0.112</v>
-      </c>
-      <c r="F2">
-        <v>-0.2</v>
+        <v>0.172</v>
       </c>
       <c r="G2">
-        <v>0.01375805320960043</v>
+        <v>0.0344011616707908</v>
       </c>
       <c r="H2">
-        <v>0.01373635544280135</v>
+        <v>0.03437597238068426</v>
       </c>
       <c r="I2">
-        <v>0.01049949371877469</v>
+        <v>0.04373305279378862</v>
       </c>
       <c r="J2">
-        <v>0.008166452278091317</v>
+        <v>0.034380273850998</v>
       </c>
       <c r="K2">
-        <v>588.46</v>
+        <v>269.7</v>
       </c>
       <c r="L2">
-        <v>0.3273914833483549</v>
+        <v>0.1998103394627272</v>
       </c>
       <c r="M2">
-        <v>331.728</v>
+        <v>153.894</v>
       </c>
       <c r="N2">
-        <v>0.05762067707700057</v>
+        <v>0.05618640447756289</v>
       </c>
       <c r="O2">
-        <v>0.5637222580974067</v>
+        <v>0.5706117908787542</v>
       </c>
       <c r="P2">
-        <v>239.27</v>
+        <v>144.75</v>
       </c>
       <c r="Q2">
-        <v>0.04156085529172673</v>
+        <v>0.05284794760112304</v>
       </c>
       <c r="R2">
-        <v>0.406603677395235</v>
+        <v>0.5367074527252503</v>
       </c>
       <c r="S2">
-        <v>92.45800000000001</v>
+        <v>9.144000000000002</v>
       </c>
       <c r="T2">
-        <v>0.2787162976896735</v>
+        <v>0.05941752115092207</v>
       </c>
       <c r="U2">
-        <v>2198.35</v>
+        <v>1173.626</v>
       </c>
       <c r="V2">
-        <v>0.3818502370985392</v>
+        <v>0.4284886034633203</v>
       </c>
       <c r="W2">
-        <v>0.1947263017356475</v>
+        <v>0.1387004456955196</v>
       </c>
       <c r="X2">
-        <v>0.03166130773823631</v>
+        <v>0.07139954231033349</v>
       </c>
       <c r="Y2">
-        <v>0.1630649939974112</v>
+        <v>0.0673009033851861</v>
       </c>
       <c r="Z2">
-        <v>0.3904977193700921</v>
+        <v>0.3343725343747639</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02809142701712805</v>
+        <v>0.05125599464789926</v>
       </c>
       <c r="AC2">
-        <v>-0.02809142701712805</v>
+        <v>-0.05123545598610021</v>
       </c>
       <c r="AD2">
-        <v>3274.652</v>
+        <v>4413.196</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3274.652</v>
+        <v>4413.196</v>
       </c>
       <c r="AG2">
-        <v>1076.302</v>
+        <v>3239.57</v>
       </c>
       <c r="AH2">
-        <v>0.3625710714820336</v>
+        <v>0.6170415590422285</v>
       </c>
       <c r="AI2">
-        <v>0.5494426800752757</v>
+        <v>0.6644082106548699</v>
       </c>
       <c r="AJ2">
-        <v>0.1575060270126066</v>
+        <v>0.5418645961569342</v>
       </c>
       <c r="AK2">
-        <v>0.286128622858027</v>
+        <v>0.5923871800638911</v>
       </c>
       <c r="AL2">
-        <v>4.505</v>
+        <v>15.12</v>
       </c>
       <c r="AM2">
-        <v>-11.275</v>
+        <v>14.925</v>
       </c>
       <c r="AN2">
-        <v>124.6252093164865</v>
+        <v>56.49252432155657</v>
       </c>
       <c r="AO2">
-        <v>4.18912319644839</v>
+        <v>3.904100529100529</v>
       </c>
       <c r="AP2">
-        <v>40.96140965139291</v>
+        <v>41.46915002560164</v>
       </c>
       <c r="AQ2">
-        <v>-1.673791574279379</v>
+        <v>3.955108877721943</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Trendline Information and Communication Services Ltd. (TASE:TREN)</t>
+          <t>Guideline Group Information Technologies Ltd (TASE:GUID)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +722,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00738</v>
+        <v>0.00167</v>
       </c>
       <c r="E3">
-        <v>-0.0433</v>
+        <v>-0.133</v>
       </c>
       <c r="G3">
-        <v>0.2077155172413793</v>
+        <v>0.1421531100478469</v>
       </c>
       <c r="H3">
-        <v>0.2060344827586207</v>
+        <v>0.1401913875598086</v>
       </c>
       <c r="I3">
-        <v>0.1017241379310345</v>
+        <v>0.1162679425837321</v>
       </c>
       <c r="J3">
-        <v>0.06888962854480095</v>
+        <v>0.08672352818805909</v>
       </c>
       <c r="K3">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="L3">
-        <v>0.0521551724137931</v>
+        <v>0.07655502392344499</v>
       </c>
       <c r="M3">
-        <v>0.9880000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02714285714285715</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.8165289256198348</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.93</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02554945054945055</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7685950413223142</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.05800000000000005</v>
-      </c>
-      <c r="T3">
-        <v>0.05870445344129559</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>6.01</v>
+        <v>3.99</v>
       </c>
       <c r="V3">
-        <v>0.1651098901098901</v>
+        <v>0.1511363636363637</v>
       </c>
       <c r="W3">
-        <v>0.03878205128205128</v>
+        <v>0.04968944099378882</v>
       </c>
       <c r="X3">
-        <v>0.02446658470497684</v>
+        <v>0.05011046226015851</v>
       </c>
       <c r="Y3">
-        <v>0.01431546657707444</v>
+        <v>-0.0004210212663696977</v>
       </c>
       <c r="Z3">
-        <v>2.203228869895536</v>
+        <v>1.478913105009906</v>
       </c>
       <c r="AA3">
-        <v>0.1517796184462851</v>
+        <v>0.1282565623500166</v>
       </c>
       <c r="AB3">
-        <v>0.02442408473798589</v>
+        <v>0.05006643743566556</v>
       </c>
       <c r="AC3">
-        <v>0.1273555337082992</v>
+        <v>0.07819012491435104</v>
       </c>
       <c r="AD3">
-        <v>0.842</v>
+        <v>0.166</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.842</v>
+        <v>0.166</v>
       </c>
       <c r="AG3">
-        <v>-5.168</v>
+        <v>-3.824</v>
       </c>
       <c r="AH3">
-        <v>0.02260888244455185</v>
+        <v>0.006248588421290372</v>
       </c>
       <c r="AI3">
-        <v>0.02502823851138458</v>
+        <v>0.005242215625592118</v>
       </c>
       <c r="AJ3">
-        <v>-0.1654713114754098</v>
+        <v>-0.1693834160170092</v>
       </c>
       <c r="AK3">
-        <v>-0.1870295309785756</v>
+        <v>-0.1381702558173147</v>
       </c>
       <c r="AL3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.06499999999999999</v>
+        <v>-0.195</v>
       </c>
       <c r="AN3">
-        <v>0.3007142857142857</v>
-      </c>
-      <c r="AO3">
-        <v>393.3333333333333</v>
+        <v>0.06102941176470588</v>
       </c>
       <c r="AP3">
-        <v>-1.845714285714286</v>
+        <v>-1.405882352941177</v>
       </c>
       <c r="AQ3">
-        <v>-36.30769230769231</v>
+        <v>-12.46153846153846</v>
       </c>
     </row>
     <row r="4">
@@ -859,115 +850,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.2446264073694984</v>
+        <v>0.257905138339921</v>
       </c>
       <c r="H4">
-        <v>0.2446264073694984</v>
+        <v>0.257905138339921</v>
       </c>
       <c r="I4">
-        <v>0.1944728761514841</v>
+        <v>0.2519762845849802</v>
       </c>
       <c r="J4">
-        <v>0.149472757135036</v>
+        <v>0.1864110268613374</v>
       </c>
       <c r="K4">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="L4">
-        <v>0.13510747185261</v>
+        <v>0.1432806324110672</v>
       </c>
       <c r="M4">
-        <v>5.72</v>
+        <v>14.91</v>
       </c>
       <c r="N4">
-        <v>0.01045703839122486</v>
+        <v>0.02480039920159681</v>
       </c>
       <c r="O4">
-        <v>0.4333333333333333</v>
+        <v>1.028275862068966</v>
       </c>
       <c r="P4">
-        <v>5.72</v>
+        <v>6.38</v>
       </c>
       <c r="Q4">
-        <v>0.01045703839122486</v>
+        <v>0.01061210911510313</v>
       </c>
       <c r="R4">
-        <v>0.4333333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>8.530000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.5720992622401074</v>
       </c>
       <c r="U4">
-        <v>47.8</v>
+        <v>51.3</v>
       </c>
       <c r="V4">
-        <v>0.08738574040219378</v>
+        <v>0.08532934131736526</v>
       </c>
       <c r="W4">
-        <v>0.0728476821192053</v>
+        <v>0.07228315054835494</v>
       </c>
       <c r="X4">
-        <v>0.02440384483881267</v>
+        <v>0.05012559546649903</v>
       </c>
       <c r="Y4">
-        <v>0.04844383728039263</v>
+        <v>0.02215755508185591</v>
       </c>
       <c r="Z4">
-        <v>0.6747703570688584</v>
+        <v>0.6300977523192827</v>
       </c>
       <c r="AA4">
-        <v>0.100859785704075</v>
+        <v>0.1174571690328581</v>
       </c>
       <c r="AB4">
-        <v>0.02437826641192039</v>
+        <v>0.05006932240487769</v>
       </c>
       <c r="AC4">
-        <v>0.07648151929215463</v>
+        <v>0.06738784662798046</v>
       </c>
       <c r="AD4">
-        <v>7.81</v>
+        <v>4.83</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7.81</v>
+        <v>4.83</v>
       </c>
       <c r="AG4">
-        <v>-39.98999999999999</v>
+        <v>-46.47</v>
       </c>
       <c r="AH4">
-        <v>0.01407689118797426</v>
+        <v>0.007969902480075243</v>
       </c>
       <c r="AI4">
-        <v>0.03747420949090734</v>
+        <v>0.02508699942866047</v>
       </c>
       <c r="AJ4">
-        <v>-0.07887418394114513</v>
+        <v>-0.08377048293764533</v>
       </c>
       <c r="AK4">
-        <v>-0.2489882323641118</v>
+        <v>-0.3290377398569709</v>
       </c>
       <c r="AL4">
-        <v>0.149</v>
+        <v>1.05</v>
       </c>
       <c r="AM4">
-        <v>-1.131</v>
+        <v>1.05</v>
       </c>
       <c r="AN4">
-        <v>0.3136546184738956</v>
+        <v>0.1548076923076923</v>
       </c>
       <c r="AO4">
-        <v>127.5167785234899</v>
+        <v>24.28571428571428</v>
       </c>
       <c r="AP4">
-        <v>-1.606024096385542</v>
+        <v>-1.489423076923077</v>
       </c>
       <c r="AQ4">
-        <v>-16.79929266136163</v>
+        <v>24.28571428571428</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plus500 Ltd. (LSE:PLUS)</t>
+          <t>Michlol Finance Ltd (TASE:MCLL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -986,116 +977,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.16</v>
-      </c>
-      <c r="E5">
-        <v>0.28</v>
-      </c>
-      <c r="F5">
-        <v>-0.2</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.4141592920353982</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.4141592920353982</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.747787610619469</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.5506784660766961</v>
       </c>
       <c r="K5">
-        <v>345.2</v>
+        <v>7.18</v>
       </c>
       <c r="L5">
-        <v>0.5314857582755966</v>
+        <v>0.3176991150442477</v>
       </c>
       <c r="M5">
-        <v>234</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1268705270006506</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.6778679026651216</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>141.6</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.07677293428757319</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4101969872537659</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="T5">
-        <v>0.3948717948717949</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>722.5</v>
+        <v>1.38</v>
       </c>
       <c r="V5">
-        <v>0.3917263066579917</v>
+        <v>0.01769230769230769</v>
       </c>
       <c r="W5">
-        <v>0.6580251620282119</v>
+        <v>0.1465306122448979</v>
       </c>
       <c r="X5">
-        <v>0.02433340642108746</v>
+        <v>0.07162369163031648</v>
       </c>
       <c r="Y5">
-        <v>0.6336917556071244</v>
+        <v>0.07490692061458146</v>
       </c>
       <c r="Z5">
-        <v>-11.12157534246576</v>
+        <v>0.1341724056043695</v>
       </c>
       <c r="AA5">
-        <v>-0</v>
+        <v>0.0738858545080345</v>
       </c>
       <c r="AB5">
-        <v>0.02432586328821064</v>
+        <v>0.05125154303230905</v>
       </c>
       <c r="AC5">
-        <v>-0.02432586328821064</v>
+        <v>0.02263431147572546</v>
       </c>
       <c r="AD5">
-        <v>8</v>
+        <v>194.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8</v>
+        <v>194.1</v>
       </c>
       <c r="AG5">
-        <v>-714.5</v>
+        <v>192.72</v>
       </c>
       <c r="AH5">
-        <v>0.004318721658389117</v>
+        <v>0.713340683572216</v>
       </c>
       <c r="AI5">
-        <v>0.01322095521401421</v>
+        <v>0.78582995951417</v>
       </c>
       <c r="AJ5">
-        <v>-0.6323568457385609</v>
+        <v>0.7118794326241134</v>
       </c>
       <c r="AK5">
-        <v>6.086030664395231</v>
+        <v>0.7846266590668513</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="AM5">
-        <v>-14.4</v>
+        <v>5.91</v>
+      </c>
+      <c r="AN5">
+        <v>10.78333333333333</v>
+      </c>
+      <c r="AO5">
+        <v>2.859560067681895</v>
+      </c>
+      <c r="AP5">
+        <v>10.70666666666667</v>
       </c>
       <c r="AQ5">
-        <v>-0</v>
+        <v>2.859560067681895</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Isracard Ltd. (TASE:ISCD)</t>
+          <t>Group Psagot for Finance and Investments Ltd (TASE:GPST)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,109 +1103,115 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.06150000000000001</v>
-      </c>
-      <c r="E6">
-        <v>0.00331</v>
+        <v>1.257</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.07776699029126213</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.07776699029126213</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.1378640776699029</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.1378640776699029</v>
       </c>
       <c r="K6">
-        <v>75.59999999999999</v>
+        <v>2.99</v>
       </c>
       <c r="L6">
-        <v>0.1132075471698113</v>
+        <v>0.02902912621359224</v>
       </c>
       <c r="M6">
-        <v>8.68</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.008782758271779824</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1148148148148148</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>8.68</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.008782758271779824</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1148148148148148</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>1224.9</v>
+        <v>16.8</v>
       </c>
       <c r="V6">
-        <v>1.239400991601741</v>
+        <v>0.2688</v>
       </c>
       <c r="W6">
-        <v>0.1041178900977827</v>
+        <v>0.06028225806451613</v>
       </c>
       <c r="X6">
-        <v>0.02718642285947541</v>
+        <v>0.08545930516269003</v>
       </c>
       <c r="Y6">
-        <v>0.07693146723830725</v>
+        <v>-0.02517704709817389</v>
       </c>
       <c r="Z6">
-        <v>0.2989524576954069</v>
+        <v>0.5573593073593073</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.07683982683982683</v>
       </c>
       <c r="AB6">
-        <v>0.02585598724215114</v>
+        <v>0.05616535244949007</v>
       </c>
       <c r="AC6">
-        <v>-0.02585598724215114</v>
+        <v>0.02067447439033676</v>
       </c>
       <c r="AD6">
-        <v>402.2</v>
+        <v>255.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>402.2</v>
+        <v>255.3</v>
       </c>
       <c r="AG6">
-        <v>-822.7</v>
+        <v>238.5</v>
       </c>
       <c r="AH6">
-        <v>0.2892484717727436</v>
+        <v>0.8033354310887351</v>
       </c>
       <c r="AI6">
-        <v>0.3227152371018214</v>
+        <v>0.7968164794007492</v>
       </c>
       <c r="AJ6">
-        <v>-4.967995169082129</v>
+        <v>0.792358803986711</v>
       </c>
       <c r="AK6">
-        <v>-38.4439252336449</v>
+        <v>0.7855731225296442</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>8.16</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>8.16</v>
+      </c>
+      <c r="AN6">
+        <v>9.744274809160306</v>
+      </c>
+      <c r="AO6">
+        <v>1.740196078431372</v>
+      </c>
+      <c r="AP6">
+        <v>9.103053435114504</v>
+      </c>
+      <c r="AQ6">
+        <v>1.740196078431372</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blender Financial Technologies (TASE:BLND)</t>
+          <t>Isracard Ltd. (TASE:ISCD)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1236,6 +1230,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.076</v>
+      </c>
+      <c r="E7">
+        <v>-0.0599</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1249,82 +1249,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-8.07</v>
+        <v>55.9</v>
       </c>
       <c r="L7">
-        <v>-2.204918032786885</v>
+        <v>0.08206106870229007</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>41.8</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.07200689061154177</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.7477638640429338</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>41.8</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.07200689061154177</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.7477638640429338</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>23.2</v>
+        <v>1043.1</v>
       </c>
       <c r="V7">
-        <v>0.3596899224806202</v>
+        <v>1.796899224806201</v>
       </c>
       <c r="W7">
-        <v>-8.658798283261802</v>
+        <v>0.06622438099751214</v>
       </c>
       <c r="X7">
-        <v>0.02598354953163761</v>
+        <v>0.0539468248809558</v>
       </c>
       <c r="Y7">
-        <v>-8.684781832793441</v>
+        <v>0.01227755611655634</v>
       </c>
       <c r="Z7">
-        <v>0.3278982261243505</v>
+        <v>31.83177570093478</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.02646382082427642</v>
+        <v>0.05057525210356946</v>
       </c>
       <c r="AC7">
-        <v>-0.02646382082427642</v>
+        <v>-0.05057525210356946</v>
       </c>
       <c r="AD7">
-        <v>15.3</v>
+        <v>260.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>15.3</v>
+        <v>260.6</v>
       </c>
       <c r="AG7">
-        <v>-7.899999999999999</v>
+        <v>-782.4999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.1917293233082707</v>
+        <v>0.3098323623825943</v>
       </c>
       <c r="AI7">
-        <v>0.3825</v>
+        <v>0.2494257274119449</v>
       </c>
       <c r="AJ7">
-        <v>-0.1395759717314487</v>
+        <v>3.873762376237625</v>
       </c>
       <c r="AK7">
-        <v>-0.4702380952380951</v>
+        <v>-460.2941176470156</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1341,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Menif Financial Services, Ltd. (TASE:MNIF)</t>
+          <t>Opal Balance Investments Ltd (TASE:OPAL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1349,6 +1352,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.16</v>
+      </c>
+      <c r="E8">
+        <v>0.162</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1362,28 +1371,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>8.74</v>
+        <v>8.15</v>
       </c>
       <c r="L8">
-        <v>0.3189781021897811</v>
+        <v>0.4335106382978723</v>
       </c>
       <c r="M8">
-        <v>4.74</v>
+        <v>4.37</v>
       </c>
       <c r="N8">
-        <v>0.02631871182676291</v>
+        <v>0.07761989342806395</v>
       </c>
       <c r="O8">
-        <v>0.5423340961098398</v>
+        <v>0.5361963190184049</v>
       </c>
       <c r="P8">
-        <v>4.74</v>
+        <v>4.37</v>
       </c>
       <c r="Q8">
-        <v>0.02631871182676291</v>
+        <v>0.07761989342806395</v>
       </c>
       <c r="R8">
-        <v>0.5423340961098398</v>
+        <v>0.5361963190184049</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1392,55 +1401,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>7.9</v>
+        <v>6.35</v>
       </c>
       <c r="V8">
-        <v>0.04386451971127152</v>
+        <v>0.1127886323268206</v>
       </c>
       <c r="W8">
-        <v>0.508139534883721</v>
+        <v>0.1484517304189436</v>
       </c>
       <c r="X8">
-        <v>0.03239596277794293</v>
+        <v>0.0655120234897387</v>
       </c>
       <c r="Y8">
-        <v>0.4757435721057781</v>
+        <v>0.08293970692920485</v>
       </c>
       <c r="Z8">
-        <v>0.1413055810547379</v>
+        <v>0.1572037795802325</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.02716593162990991</v>
+        <v>0.05112981997678492</v>
       </c>
       <c r="AC8">
-        <v>-0.02716593162990991</v>
+        <v>-0.05112981997678492</v>
       </c>
       <c r="AD8">
-        <v>205.7</v>
+        <v>100.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>205.7</v>
+        <v>100.4</v>
       </c>
       <c r="AG8">
-        <v>197.8</v>
+        <v>94.05000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.533177812337999</v>
+        <v>0.6407147415443524</v>
       </c>
       <c r="AI8">
-        <v>0.6923594749242679</v>
+        <v>0.6519480519480519</v>
       </c>
       <c r="AJ8">
-        <v>0.5234188938872717</v>
+        <v>0.6255404057199867</v>
       </c>
       <c r="AK8">
-        <v>0.6839557399723375</v>
+        <v>0.6369793430409754</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1457,7 +1466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.L.R.N Projects and Trade Ltd. (TASE:MLRN)</t>
+          <t>Peninsula Group Ltd (TASE:PEN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1465,6 +1474,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.197</v>
+      </c>
+      <c r="E9">
+        <v>0.206</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1478,28 +1493,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>7.45</v>
+        <v>13</v>
       </c>
       <c r="L9">
-        <v>0.4745222929936306</v>
+        <v>0.4676258992805755</v>
       </c>
       <c r="M9">
-        <v>2.98</v>
+        <v>10.1</v>
       </c>
       <c r="N9">
-        <v>0.0223555888972243</v>
+        <v>0.08054226475279107</v>
       </c>
       <c r="O9">
-        <v>0.4</v>
+        <v>0.7769230769230769</v>
       </c>
       <c r="P9">
-        <v>2.98</v>
+        <v>10.1</v>
       </c>
       <c r="Q9">
-        <v>0.0223555888972243</v>
+        <v>0.08054226475279107</v>
       </c>
       <c r="R9">
-        <v>0.4</v>
+        <v>0.7769230769230769</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1508,55 +1523,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>16.3</v>
+        <v>14.2</v>
       </c>
       <c r="V9">
-        <v>0.1222805701425356</v>
+        <v>0.113237639553429</v>
       </c>
       <c r="W9">
-        <v>0.3547619047619048</v>
+        <v>0.08338678640153944</v>
       </c>
       <c r="X9">
-        <v>0.03289311925149431</v>
+        <v>0.06773572802525016</v>
       </c>
       <c r="Y9">
-        <v>0.3218687855104105</v>
+        <v>0.01565105837628929</v>
       </c>
       <c r="Z9">
-        <v>0.1859748874674248</v>
+        <v>0.08870453095086153</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.02724543474799366</v>
+        <v>0.05118064396560197</v>
       </c>
       <c r="AC9">
-        <v>-0.02724543474799366</v>
+        <v>-0.05118064396560197</v>
       </c>
       <c r="AD9">
-        <v>161.6</v>
+        <v>255.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>161.6</v>
+        <v>255.8</v>
       </c>
       <c r="AG9">
-        <v>145.3</v>
+        <v>241.6</v>
       </c>
       <c r="AH9">
-        <v>0.5479823669040352</v>
+        <v>0.6710388247639034</v>
       </c>
       <c r="AI9">
-        <v>0.8100250626566415</v>
+        <v>0.6393401649587603</v>
       </c>
       <c r="AJ9">
-        <v>0.5215362526920315</v>
+        <v>0.6583106267029973</v>
       </c>
       <c r="AK9">
-        <v>0.7931222707423581</v>
+        <v>0.626068929774553</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1573,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Peninsula Group Ltd (TASE:PEN)</t>
+          <t>S.R. Accord Ltd. (TASE:SRAC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1582,10 +1597,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.411</v>
+        <v>0.273</v>
       </c>
       <c r="E10">
-        <v>0.507</v>
+        <v>0.254</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1600,85 +1615,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>31.6</v>
+        <v>23.4</v>
       </c>
       <c r="L10">
-        <v>0.5524475524475524</v>
+        <v>0.6358695652173914</v>
       </c>
       <c r="M10">
-        <v>19.5</v>
+        <v>7.914</v>
       </c>
       <c r="N10">
-        <v>0.07862903225806452</v>
+        <v>0.05394683026584867</v>
       </c>
       <c r="O10">
-        <v>0.6170886075949367</v>
+        <v>0.3382051282051282</v>
       </c>
       <c r="P10">
-        <v>19.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q10">
-        <v>0.07862903225806452</v>
+        <v>0.04976141785957737</v>
       </c>
       <c r="R10">
-        <v>0.6170886075949367</v>
+        <v>0.311965811965812</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.6139999999999999</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.0775840283042709</v>
       </c>
       <c r="U10">
-        <v>20.1</v>
+        <v>4.74</v>
       </c>
       <c r="V10">
-        <v>0.0810483870967742</v>
+        <v>0.03231083844580777</v>
       </c>
       <c r="W10">
-        <v>0.233210332103321</v>
+        <v>0.2802395209580838</v>
       </c>
       <c r="X10">
-        <v>0.02937720186981003</v>
+        <v>0.07013148011843401</v>
       </c>
       <c r="Y10">
-        <v>0.203833130233511</v>
+        <v>0.2101080408396498</v>
       </c>
       <c r="Z10">
-        <v>0.2543352601156069</v>
+        <v>0.1192868719611021</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.02802739009545327</v>
+        <v>0.05122659988002292</v>
       </c>
       <c r="AC10">
-        <v>-0.02802739009545327</v>
+        <v>-0.05122659988002292</v>
       </c>
       <c r="AD10">
-        <v>177.6</v>
+        <v>339.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>177.6</v>
+        <v>339.8</v>
       </c>
       <c r="AG10">
-        <v>157.5</v>
+        <v>335.06</v>
       </c>
       <c r="AH10">
-        <v>0.4172932330827067</v>
+        <v>0.6984583761562179</v>
       </c>
       <c r="AI10">
-        <v>0.5325337331334332</v>
+        <v>0.7874855156431054</v>
       </c>
       <c r="AJ10">
-        <v>0.3884093711467324</v>
+        <v>0.6954915310528064</v>
       </c>
       <c r="AK10">
-        <v>0.5025526483726867</v>
+        <v>0.785125128878058</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1695,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Opal Balance Investments Ltd (TASE:OPAL)</t>
+          <t>Menif - Financial Services Ltd (TASE:MNIF)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1703,12 +1718,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.124</v>
-      </c>
-      <c r="E11">
-        <v>0.112</v>
-      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1722,28 +1731,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>7.57</v>
+        <v>22.7</v>
       </c>
       <c r="L11">
-        <v>0.4426900584795321</v>
+        <v>0.6735905044510385</v>
       </c>
       <c r="M11">
-        <v>3.72</v>
+        <v>12.3</v>
       </c>
       <c r="N11">
-        <v>0.03907563025210084</v>
+        <v>0.07899807321772641</v>
       </c>
       <c r="O11">
-        <v>0.4914134742404228</v>
+        <v>0.5418502202643173</v>
       </c>
       <c r="P11">
-        <v>3.72</v>
+        <v>12.3</v>
       </c>
       <c r="Q11">
-        <v>0.03907563025210084</v>
+        <v>0.07899807321772641</v>
       </c>
       <c r="R11">
-        <v>0.4914134742404228</v>
+        <v>0.5418502202643173</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1752,55 +1761,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>7.61</v>
+        <v>5.65</v>
       </c>
       <c r="V11">
-        <v>0.07993697478991597</v>
+        <v>0.03628773281952473</v>
       </c>
       <c r="W11">
-        <v>0.1570539419087137</v>
+        <v>0.2489035087719298</v>
       </c>
       <c r="X11">
-        <v>0.02968420349747138</v>
+        <v>0.07117539299035051</v>
       </c>
       <c r="Y11">
-        <v>0.1273697384112423</v>
+        <v>0.1777281157815793</v>
       </c>
       <c r="Z11">
-        <v>0.2047904191616767</v>
+        <v>0.1166089965397924</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.02815546393880283</v>
+        <v>0.0512443120921775</v>
       </c>
       <c r="AC11">
-        <v>-0.02815546393880283</v>
+        <v>-0.0512443120921775</v>
       </c>
       <c r="AD11">
-        <v>72.3</v>
+        <v>379.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>72.3</v>
+        <v>379.4</v>
       </c>
       <c r="AG11">
-        <v>64.69</v>
+        <v>373.75</v>
       </c>
       <c r="AH11">
-        <v>0.4316417910447761</v>
+        <v>0.7090263502149132</v>
       </c>
       <c r="AI11">
-        <v>0.5683962264150944</v>
+        <v>0.8005908419497785</v>
       </c>
       <c r="AJ11">
-        <v>0.4045906560760523</v>
+        <v>0.7059212390216262</v>
       </c>
       <c r="AK11">
-        <v>0.5409315160130446</v>
+        <v>0.798184730379071</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1817,7 +1826,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S.R. Accord Ltd. (TASE:SRAC)</t>
+          <t>Direct Finance of Direct Group (2006) Ltd (TASE:DIFI)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1825,12 +1834,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.196</v>
-      </c>
-      <c r="E12">
-        <v>0.117</v>
-      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1844,28 +1847,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>19.9</v>
+        <v>66.5</v>
       </c>
       <c r="L12">
-        <v>0.5922619047619047</v>
+        <v>0.3674033149171271</v>
       </c>
       <c r="M12">
-        <v>10.5</v>
+        <v>33.9</v>
       </c>
       <c r="N12">
-        <v>0.04629629629629629</v>
+        <v>0.07208165001063151</v>
       </c>
       <c r="O12">
-        <v>0.5276381909547739</v>
+        <v>0.5097744360902255</v>
       </c>
       <c r="P12">
-        <v>10.5</v>
+        <v>33.9</v>
       </c>
       <c r="Q12">
-        <v>0.04629629629629629</v>
+        <v>0.07208165001063151</v>
       </c>
       <c r="R12">
-        <v>0.5276381909547739</v>
+        <v>0.5097744360902255</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1874,55 +1877,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>11.6</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="V12">
-        <v>0.05114638447971781</v>
+        <v>0.01730810121199235</v>
       </c>
       <c r="W12">
-        <v>0.2855093256814921</v>
+        <v>0.274793388429752</v>
       </c>
       <c r="X12">
-        <v>0.03169491526227389</v>
+        <v>0.07219455391486097</v>
       </c>
       <c r="Y12">
-        <v>0.2538144104192182</v>
+        <v>0.2025988345148911</v>
       </c>
       <c r="Z12">
-        <v>0.1673640167364017</v>
+        <v>0.166651321241138</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0288600053786653</v>
+        <v>0.05126044626348948</v>
       </c>
       <c r="AC12">
-        <v>-0.0288600053786653</v>
+        <v>-0.05126044626348948</v>
       </c>
       <c r="AD12">
-        <v>236.6</v>
+        <v>1201.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>236.6</v>
+        <v>1201.3</v>
       </c>
       <c r="AG12">
-        <v>225</v>
+        <v>1193.16</v>
       </c>
       <c r="AH12">
-        <v>0.5105740181268882</v>
+        <v>0.7186527877482651</v>
       </c>
       <c r="AI12">
-        <v>0.7391440174945328</v>
+        <v>0.7861910994764397</v>
       </c>
       <c r="AJ12">
-        <v>0.49800796812749</v>
+        <v>0.7172760390992269</v>
       </c>
       <c r="AK12">
-        <v>0.7293354943273906</v>
+        <v>0.7850459910781256</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1939,7 +1942,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michman Besd Ltd (TASE:MCMN)</t>
+          <t>Gamla - Harel Residential Real-Estate Ltd (TASE:GMLA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1960,82 +1963,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>6.35</v>
+        <v>7.97</v>
       </c>
       <c r="L13">
-        <v>0.9176300578034682</v>
+        <v>0.6083969465648855</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>3.03</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.0461890243902439</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.3801756587202008</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>3.03</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.0461890243902439</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.3801756587202008</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>1.47</v>
+        <v>0.099</v>
       </c>
       <c r="V13">
-        <v>0.02155425219941349</v>
+        <v>0.001509146341463415</v>
       </c>
       <c r="W13">
-        <v>1.74931129476584</v>
+        <v>0.1308702791461412</v>
       </c>
       <c r="X13">
-        <v>0.03162770021419872</v>
+        <v>0.07657251216451358</v>
       </c>
       <c r="Y13">
-        <v>1.717683594551642</v>
+        <v>0.05429776698162764</v>
       </c>
       <c r="Z13">
-        <v>0.3420493302357768</v>
+        <v>0.09214774589731504</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03003206904122095</v>
+        <v>0.05131912145649137</v>
       </c>
       <c r="AC13">
-        <v>-0.03003206904122095</v>
+        <v>-0.05131912145649137</v>
       </c>
       <c r="AD13">
-        <v>70.5</v>
+        <v>200.7</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>70.5</v>
+        <v>200.7</v>
       </c>
       <c r="AG13">
-        <v>69.03</v>
+        <v>200.601</v>
       </c>
       <c r="AH13">
-        <v>0.5082912761355444</v>
+        <v>0.7536612842658656</v>
       </c>
       <c r="AI13">
-        <v>0.7842046718576196</v>
+        <v>0.7375964718853362</v>
       </c>
       <c r="AJ13">
-        <v>0.5030241200903592</v>
+        <v>0.7535696710380502</v>
       </c>
       <c r="AK13">
-        <v>0.7806174375212032</v>
+        <v>0.7375009650699814</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2052,7 +2058,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Direct Finance of Direct Group (2006) Ltd (TASE:DIFI)</t>
+          <t>Nawi Brothers Group Ltd (TASE:NAWI)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2060,6 +2066,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.158</v>
+      </c>
+      <c r="E14">
+        <v>0.182</v>
+      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2073,28 +2085,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>56.1</v>
+        <v>39.3</v>
       </c>
       <c r="L14">
-        <v>0.4434782608695652</v>
+        <v>0.6943462897526501</v>
       </c>
       <c r="M14">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="N14">
-        <v>0.02629611166500499</v>
+        <v>0.09388646288209607</v>
       </c>
       <c r="O14">
-        <v>0.376114081996435</v>
+        <v>0.5470737913486006</v>
       </c>
       <c r="P14">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="Q14">
-        <v>0.02629611166500499</v>
+        <v>0.09388646288209607</v>
       </c>
       <c r="R14">
-        <v>0.376114081996435</v>
+        <v>0.5470737913486006</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2103,55 +2115,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>51.3</v>
+        <v>0.526</v>
       </c>
       <c r="V14">
-        <v>0.06393320039880358</v>
+        <v>0.002296943231441048</v>
       </c>
       <c r="W14">
-        <v>0.2926447574334898</v>
+        <v>0.2024729520865533</v>
       </c>
       <c r="X14">
-        <v>0.03221001784432908</v>
+        <v>0.0785286890331332</v>
       </c>
       <c r="Y14">
-        <v>0.2604347395891607</v>
+        <v>0.1239442630534201</v>
       </c>
       <c r="Z14">
-        <v>0.1398299932572098</v>
+        <v>0.06155586248898846</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.03024732935262098</v>
+        <v>0.05134086759238156</v>
       </c>
       <c r="AC14">
-        <v>-0.03024732935262098</v>
+        <v>-0.05134086759238156</v>
       </c>
       <c r="AD14">
-        <v>895.4</v>
+        <v>752.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>895.4</v>
+        <v>752.3</v>
       </c>
       <c r="AG14">
-        <v>844.1</v>
+        <v>751.774</v>
       </c>
       <c r="AH14">
-        <v>0.5273883849687832</v>
+        <v>0.7666360949760521</v>
       </c>
       <c r="AI14">
-        <v>0.7872340425531914</v>
+        <v>0.7982809847198642</v>
       </c>
       <c r="AJ14">
-        <v>0.5126632250227756</v>
+        <v>0.7665109393193539</v>
       </c>
       <c r="AK14">
-        <v>0.7771844213240034</v>
+        <v>0.79816833249458</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2168,7 +2180,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nawi Brothers Group Ltd (TASE:NAWI)</t>
+          <t>Michman Besd Ltd (TASE:MCMN)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2176,12 +2188,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.11</v>
-      </c>
-      <c r="E15">
-        <v>0.09080000000000001</v>
-      </c>
       <c r="G15">
         <v>0</v>
       </c>
@@ -2195,85 +2201,82 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>30.6</v>
+        <v>3.06</v>
       </c>
       <c r="L15">
-        <v>0.6710526315789473</v>
+        <v>0.1738636363636364</v>
       </c>
       <c r="M15">
-        <v>19.8</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.05901639344262295</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.6470588235294118</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>19.8</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.05901639344262295</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.6470588235294118</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>5.76</v>
       </c>
       <c r="V15">
-        <v>0.00301043219076006</v>
+        <v>0.07944827586206896</v>
       </c>
       <c r="W15">
-        <v>0.1787383177570094</v>
+        <v>0.1577319587628866</v>
       </c>
       <c r="X15">
-        <v>0.03964488126658006</v>
+        <v>0.06994843685612159</v>
       </c>
       <c r="Y15">
-        <v>0.1390934364904293</v>
+        <v>0.08778352190676503</v>
       </c>
       <c r="Z15">
-        <v>0.09598787521576223</v>
+        <v>0.1990274793622074</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03040849665067573</v>
+        <v>0.05535306186441299</v>
       </c>
       <c r="AC15">
-        <v>-0.03040849665067573</v>
+        <v>-0.05535306186441299</v>
       </c>
       <c r="AD15">
-        <v>726.4</v>
+        <v>166.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>726.4</v>
+        <v>166.4</v>
       </c>
       <c r="AG15">
-        <v>725.39</v>
+        <v>160.64</v>
       </c>
       <c r="AH15">
-        <v>0.6840568791788303</v>
+        <v>0.6965257429886982</v>
       </c>
       <c r="AI15">
-        <v>0.7891363389462248</v>
+        <v>0.8590604026845637</v>
       </c>
       <c r="AJ15">
-        <v>0.6837560915834818</v>
+        <v>0.6890280518143604</v>
       </c>
       <c r="AK15">
-        <v>0.788904718920271</v>
+        <v>0.8547408747472597</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2290,7 +2293,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gibui Holdings Ltd (TASE:GIBUI)</t>
+          <t>Blender Financial Technologies (TASE:BLND)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2311,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>2.36</v>
+        <v>-6.96</v>
       </c>
       <c r="L16">
-        <v>0.3017902813299232</v>
+        <v>-1.669064748201439</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2323,7 +2326,7 @@
         <v>-0</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2332,61 +2335,61 @@
         <v>-0</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="U16">
-        <v>8.15</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>0.1643145161290323</v>
+        <v>0.9513742071881606</v>
       </c>
       <c r="W16">
-        <v>0.2107142857142857</v>
+        <v>-0.2817813765182186</v>
       </c>
       <c r="X16">
-        <v>0.03637468281388748</v>
+        <v>0.07231921560583626</v>
       </c>
       <c r="Y16">
-        <v>0.1743396029003982</v>
+        <v>-0.3541005921240549</v>
       </c>
       <c r="Z16">
-        <v>0.1743201069995542</v>
+        <v>0.2482142857142857</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.0314053840706006</v>
+        <v>0.05552996230265501</v>
       </c>
       <c r="AC16">
-        <v>-0.0314053840706006</v>
+        <v>-0.05552996230265501</v>
       </c>
       <c r="AD16">
-        <v>84.5</v>
+        <v>24.3</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>84.5</v>
+        <v>24.3</v>
       </c>
       <c r="AG16">
-        <v>76.34999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="AH16">
-        <v>0.6301267710663684</v>
+        <v>0.7197867298578198</v>
       </c>
       <c r="AI16">
-        <v>0.7853159851301116</v>
+        <v>0.6014851485148515</v>
       </c>
       <c r="AJ16">
-        <v>0.6061929337038507</v>
+        <v>0.6179321486268174</v>
       </c>
       <c r="AK16">
-        <v>0.7677224736048266</v>
+        <v>0.4872611464968153</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2403,7 +2406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unet Credit Finance Services Ltd (TASE:UNCR)</t>
+          <t>M.L.R.N Projects and Trade Ltd. (TASE:MLRN)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2412,112 +2415,103 @@
         </is>
       </c>
       <c r="G17">
-        <v>-0.214987714987715</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>-0.214987714987715</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>-0.07837837837837837</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>-0.07837837837837837</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>-3.58</v>
+        <v>11.8</v>
       </c>
       <c r="L17">
-        <v>-0.4398034398034398</v>
+        <v>0.4169611307420495</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>4.07</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>0.3449152542372881</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>4.07</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>0.3449152542372881</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>9.9</v>
+        <v>1.78</v>
       </c>
       <c r="V17">
-        <v>0.3626373626373626</v>
+        <v>0.03236363636363637</v>
       </c>
       <c r="W17">
-        <v>-0.3627152988855117</v>
+        <v>0.3113456464379947</v>
       </c>
       <c r="X17">
-        <v>0.0336728777588095</v>
+        <v>0.09053916702470005</v>
       </c>
       <c r="Y17">
-        <v>-0.3963881766443212</v>
+        <v>0.2208064794132947</v>
       </c>
       <c r="Z17">
-        <v>0.3536055603822764</v>
+        <v>0.1544759825327511</v>
       </c>
       <c r="AA17">
-        <v>-0.02771503040834058</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.02938508604606787</v>
+        <v>0.05631993222401549</v>
       </c>
       <c r="AC17">
-        <v>-0.05710011645440845</v>
+        <v>-0.05631993222401549</v>
       </c>
       <c r="AD17">
-        <v>36.1</v>
+        <v>256.9</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>36.1</v>
+        <v>256.9</v>
       </c>
       <c r="AG17">
-        <v>26.2</v>
+        <v>255.12</v>
       </c>
       <c r="AH17">
-        <v>0.5694006309148265</v>
+        <v>0.8236614299454953</v>
       </c>
       <c r="AI17">
-        <v>0.6036789297658863</v>
+        <v>0.7703148425787105</v>
       </c>
       <c r="AJ17">
-        <v>0.4897196261682243</v>
+        <v>0.8226492970463045</v>
       </c>
       <c r="AK17">
-        <v>0.5250501002004008</v>
+        <v>0.7690823586157</v>
       </c>
       <c r="AL17">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>2.56</v>
-      </c>
-      <c r="AN17">
-        <v>-67.60299625468164</v>
-      </c>
-      <c r="AO17">
-        <v>-0.24921875</v>
-      </c>
-      <c r="AP17">
-        <v>-49.06367041198502</v>
-      </c>
-      <c r="AQ17">
-        <v>-0.24921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2528,7 +2522,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Value Capital One Ltd (TASE:VALU)</t>
+          <t>Erech Finance Cahalacha Ltd (TASE:EFNC)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2536,26 +2530,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.357</v>
-      </c>
       <c r="G18">
-        <v>-0.2338204592901879</v>
+        <v>-0.002325581395348838</v>
       </c>
       <c r="H18">
-        <v>-0.2338204592901879</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>-0.1931106471816284</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>-0.1931106471816284</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>-5.77</v>
+        <v>-1.39</v>
       </c>
       <c r="L18">
-        <v>-0.6022964509394572</v>
+        <v>-0.4617940199335548</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2579,73 +2570,61 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>38.6</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="V18">
-        <v>0.3505903723887375</v>
+        <v>0.1830699774266366</v>
       </c>
       <c r="W18">
-        <v>-9.965457685664939</v>
+        <v>-0.09928571428571428</v>
       </c>
       <c r="X18">
-        <v>0.03548847157780926</v>
+        <v>0.09094586052601639</v>
       </c>
       <c r="Y18">
-        <v>-10.00094615724275</v>
+        <v>-0.1902315748117307</v>
       </c>
       <c r="Z18">
-        <v>1.684839957791066</v>
+        <v>0.1454106280193236</v>
       </c>
       <c r="AA18">
-        <v>-0.3253605346465002</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.03120317352635991</v>
+        <v>0.05633093774006873</v>
       </c>
       <c r="AC18">
-        <v>-0.3565637081728601</v>
+        <v>-0.05633093774006873</v>
       </c>
       <c r="AD18">
-        <v>173.8</v>
+        <v>20.9</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>173.8</v>
+        <v>20.9</v>
       </c>
       <c r="AG18">
-        <v>135.2</v>
+        <v>20.089</v>
       </c>
       <c r="AH18">
-        <v>0.6121873899260304</v>
+        <v>0.8251085669166995</v>
       </c>
       <c r="AI18">
-        <v>0.7430525865754596</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="AJ18">
-        <v>0.5511618426416633</v>
+        <v>0.8193237897140992</v>
       </c>
       <c r="AK18">
-        <v>0.692268305171531</v>
+        <v>0.5660627236608526</v>
       </c>
       <c r="AL18">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1.761</v>
-      </c>
-      <c r="AN18">
-        <v>-195.2808988764045</v>
-      </c>
-      <c r="AO18">
-        <v>-1.033519553072626</v>
-      </c>
-      <c r="AP18">
-        <v>-151.9101123595506</v>
-      </c>
-      <c r="AQ18">
-        <v>-1.050539466212379</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AQ21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.16</v>
+        <v>0.127</v>
       </c>
       <c r="E2">
-        <v>0.172</v>
+        <v>0.146</v>
       </c>
       <c r="G2">
-        <v>0.0344011616707908</v>
+        <v>0.04991085293610169</v>
       </c>
       <c r="H2">
-        <v>0.03437597238068426</v>
+        <v>0.04570464523302851</v>
       </c>
       <c r="I2">
-        <v>0.04373305279378862</v>
+        <v>0.04480806221762108</v>
       </c>
       <c r="J2">
-        <v>0.034380273850998</v>
+        <v>0.03610729075909647</v>
       </c>
       <c r="K2">
-        <v>269.7</v>
+        <v>265.224</v>
       </c>
       <c r="L2">
-        <v>0.1998103394627272</v>
+        <v>0.1694906155940262</v>
       </c>
       <c r="M2">
-        <v>153.894</v>
+        <v>145.364</v>
       </c>
       <c r="N2">
-        <v>0.05618640447756289</v>
+        <v>0.05098916825681895</v>
       </c>
       <c r="O2">
-        <v>0.5706117908787542</v>
+        <v>0.5480801134135674</v>
       </c>
       <c r="P2">
-        <v>144.75</v>
+        <v>96.77</v>
       </c>
       <c r="Q2">
-        <v>0.05284794760112304</v>
+        <v>0.03394390503984734</v>
       </c>
       <c r="R2">
-        <v>0.5367074527252503</v>
+        <v>0.3648614001749464</v>
       </c>
       <c r="S2">
-        <v>9.144000000000002</v>
+        <v>48.594</v>
       </c>
       <c r="T2">
-        <v>0.05941752115092207</v>
+        <v>0.3342918466745549</v>
       </c>
       <c r="U2">
-        <v>1173.626</v>
+        <v>408.514</v>
       </c>
       <c r="V2">
-        <v>0.4284886034633203</v>
+        <v>0.1432940004489842</v>
       </c>
       <c r="W2">
-        <v>0.1387004456955196</v>
+        <v>0.1365166819712274</v>
       </c>
       <c r="X2">
-        <v>0.07139954231033349</v>
+        <v>0.07714946846229298</v>
       </c>
       <c r="Y2">
-        <v>0.0673009033851861</v>
+        <v>0.05936721350893445</v>
       </c>
       <c r="Z2">
-        <v>0.3343725343747639</v>
+        <v>0.2850109827663457</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05125599464789926</v>
+        <v>0.05426517214240925</v>
       </c>
       <c r="AC2">
-        <v>-0.05123545598610021</v>
+        <v>-0.05352284731313342</v>
       </c>
       <c r="AD2">
-        <v>4413.196</v>
+        <v>5063.144</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4413.196</v>
+        <v>5063.144</v>
       </c>
       <c r="AG2">
-        <v>3239.57</v>
+        <v>4654.63</v>
       </c>
       <c r="AH2">
-        <v>0.6170415590422285</v>
+        <v>0.6397685930697203</v>
       </c>
       <c r="AI2">
-        <v>0.6644082106548699</v>
+        <v>0.6887221988861054</v>
       </c>
       <c r="AJ2">
-        <v>0.5418645961569342</v>
+        <v>0.6201617211888333</v>
       </c>
       <c r="AK2">
-        <v>0.5923871800638911</v>
+        <v>0.6704071300693217</v>
       </c>
       <c r="AL2">
-        <v>15.12</v>
+        <v>27.421</v>
       </c>
       <c r="AM2">
-        <v>14.925</v>
+        <v>22.762</v>
       </c>
       <c r="AN2">
-        <v>56.49252432155657</v>
+        <v>55.9655130486686</v>
       </c>
       <c r="AO2">
-        <v>3.904100529100529</v>
+        <v>2.557054812005397</v>
       </c>
       <c r="AP2">
-        <v>41.46915002560164</v>
+        <v>51.44999944732449</v>
       </c>
       <c r="AQ2">
-        <v>3.955108877721943</v>
+        <v>3.08044108602056</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guideline Group Information Technologies Ltd (TASE:GUID)</t>
+          <t>Payment Financial Technologies Ltd (TASE:PMNT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,116 +721,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.00167</v>
-      </c>
-      <c r="E3">
-        <v>-0.133</v>
-      </c>
       <c r="G3">
-        <v>0.1421531100478469</v>
+        <v>0.4386138613861386</v>
       </c>
       <c r="H3">
-        <v>0.1401913875598086</v>
+        <v>0.297029702970297</v>
       </c>
       <c r="I3">
-        <v>0.1162679425837321</v>
+        <v>0.5564356435643565</v>
       </c>
       <c r="J3">
-        <v>0.08672352818805909</v>
+        <v>0.4679580177338883</v>
       </c>
       <c r="K3">
-        <v>1.6</v>
+        <v>3.22</v>
       </c>
       <c r="L3">
-        <v>0.07655502392344499</v>
+        <v>0.3188118811881188</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.57</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03729216152019003</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.4875776397515528</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03729216152019003</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4875776397515528</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>3.99</v>
+        <v>3.69</v>
       </c>
       <c r="V3">
-        <v>0.1511363636363637</v>
+        <v>0.08764845605700712</v>
       </c>
       <c r="W3">
-        <v>0.04968944099378882</v>
+        <v>0.2175675675675676</v>
       </c>
       <c r="X3">
-        <v>0.05011046226015851</v>
+        <v>0.06032902210839954</v>
       </c>
       <c r="Y3">
-        <v>-0.0004210212663696977</v>
+        <v>0.157238545459168</v>
       </c>
       <c r="Z3">
-        <v>1.478913105009906</v>
+        <v>0.4163231657048639</v>
       </c>
       <c r="AA3">
-        <v>0.1282565623500166</v>
+        <v>0.1948217633599452</v>
       </c>
       <c r="AB3">
-        <v>0.05006643743566556</v>
+        <v>0.05456843268853141</v>
       </c>
       <c r="AC3">
-        <v>0.07819012491435104</v>
+        <v>0.1402533306714138</v>
       </c>
       <c r="AD3">
-        <v>0.166</v>
+        <v>32.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.166</v>
+        <v>32.6</v>
       </c>
       <c r="AG3">
-        <v>-3.824</v>
+        <v>28.91</v>
       </c>
       <c r="AH3">
-        <v>0.006248588421290372</v>
+        <v>0.4364123159303882</v>
       </c>
       <c r="AI3">
-        <v>0.005242215625592118</v>
+        <v>0.6735537190082644</v>
       </c>
       <c r="AJ3">
-        <v>-0.1693834160170092</v>
+        <v>0.4071257569356428</v>
       </c>
       <c r="AK3">
-        <v>-0.1381702558173147</v>
+        <v>0.6466114963095504</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AM3">
-        <v>-0.195</v>
+        <v>0.179</v>
       </c>
       <c r="AN3">
-        <v>0.06102941176470588</v>
+        <v>5.68935427574171</v>
+      </c>
+      <c r="AO3">
+        <v>31.39664804469274</v>
       </c>
       <c r="AP3">
-        <v>-1.405882352941177</v>
+        <v>5.045375218150087</v>
       </c>
       <c r="AQ3">
-        <v>-12.46153846153846</v>
+        <v>31.39664804469274</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Tel-Aviv Stock Exchange Ltd. (TASE:TASE)</t>
+          <t>Automatic Bank Services Limited (TASE:SHVA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,116 +849,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.146</v>
+      </c>
+      <c r="E4">
+        <v>0.171</v>
+      </c>
       <c r="G4">
-        <v>0.257905138339921</v>
+        <v>0.415204678362573</v>
       </c>
       <c r="H4">
-        <v>0.257905138339921</v>
+        <v>0.415204678362573</v>
       </c>
       <c r="I4">
-        <v>0.2519762845849802</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="J4">
-        <v>0.1864110268613374</v>
+        <v>0.2665110356536503</v>
       </c>
       <c r="K4">
-        <v>14.5</v>
+        <v>9.65</v>
       </c>
       <c r="L4">
-        <v>0.1432806324110672</v>
+        <v>0.2821637426900584</v>
       </c>
       <c r="M4">
-        <v>14.91</v>
+        <v>5.77</v>
       </c>
       <c r="N4">
-        <v>0.02480039920159681</v>
+        <v>0.03295259851513421</v>
       </c>
       <c r="O4">
-        <v>1.028275862068966</v>
+        <v>0.5979274611398963</v>
       </c>
       <c r="P4">
-        <v>6.38</v>
+        <v>5.77</v>
       </c>
       <c r="Q4">
-        <v>0.01061210911510313</v>
+        <v>0.03295259851513421</v>
       </c>
       <c r="R4">
-        <v>0.44</v>
+        <v>0.5979274611398963</v>
       </c>
       <c r="S4">
-        <v>8.530000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.5720992622401074</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>51.3</v>
+        <v>7.99</v>
       </c>
       <c r="V4">
-        <v>0.08532934131736526</v>
+        <v>0.04563106796116505</v>
       </c>
       <c r="W4">
-        <v>0.07228315054835494</v>
+        <v>0.1690017513134851</v>
       </c>
       <c r="X4">
-        <v>0.05012559546649903</v>
+        <v>0.05261229408691725</v>
       </c>
       <c r="Y4">
-        <v>0.02215755508185591</v>
+        <v>0.1163894572265678</v>
       </c>
       <c r="Z4">
-        <v>0.6300977523192827</v>
+        <v>0.5812372535690007</v>
       </c>
       <c r="AA4">
-        <v>0.1174571690328581</v>
+        <v>0.1549061424091577</v>
       </c>
       <c r="AB4">
-        <v>0.05006932240487769</v>
+        <v>0.05238353245530727</v>
       </c>
       <c r="AC4">
-        <v>0.06738784662798046</v>
+        <v>0.1025226099538504</v>
       </c>
       <c r="AD4">
-        <v>4.83</v>
+        <v>5.48</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4.83</v>
+        <v>5.48</v>
       </c>
       <c r="AG4">
-        <v>-46.47</v>
+        <v>-2.51</v>
       </c>
       <c r="AH4">
-        <v>0.007969902480075243</v>
+        <v>0.03034666075977407</v>
       </c>
       <c r="AI4">
-        <v>0.02508699942866047</v>
+        <v>0.08619062598301354</v>
       </c>
       <c r="AJ4">
-        <v>-0.08377048293764533</v>
+        <v>-0.01454313691407381</v>
       </c>
       <c r="AK4">
-        <v>-0.3290377398569709</v>
+        <v>-0.045152005756431</v>
       </c>
       <c r="AL4">
-        <v>1.05</v>
+        <v>0.192</v>
       </c>
       <c r="AM4">
-        <v>1.05</v>
+        <v>-0.8180000000000001</v>
       </c>
       <c r="AN4">
-        <v>0.1548076923076923</v>
+        <v>0.4151515151515152</v>
       </c>
       <c r="AO4">
-        <v>24.28571428571428</v>
+        <v>60.93749999999999</v>
       </c>
       <c r="AP4">
-        <v>-1.489423076923077</v>
+        <v>-0.1901515151515152</v>
       </c>
       <c r="AQ4">
-        <v>24.28571428571428</v>
+        <v>-14.30317848410758</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Michlol Finance Ltd (TASE:MCLL)</t>
+          <t>The Tel-Aviv Stock Exchange Ltd. (TASE:TASE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,32 +983,38 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.08839999999999999</v>
+      </c>
+      <c r="E5">
+        <v>-0.0101</v>
+      </c>
       <c r="G5">
-        <v>0.4141592920353982</v>
+        <v>0.3238289205702647</v>
       </c>
       <c r="H5">
-        <v>0.4141592920353982</v>
+        <v>0.3238289205702647</v>
       </c>
       <c r="I5">
-        <v>0.747787610619469</v>
+        <v>0.2718940936863544</v>
       </c>
       <c r="J5">
-        <v>0.5506784660766961</v>
+        <v>0.205212842573161</v>
       </c>
       <c r="K5">
-        <v>7.18</v>
+        <v>19.8</v>
       </c>
       <c r="L5">
-        <v>0.3176991150442477</v>
+        <v>0.2016293279022403</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>40.6</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.07880434782608695</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>2.050505050505051</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1014,76 +1026,79 @@
         <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>40.6</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>1.38</v>
+        <v>60.4</v>
       </c>
       <c r="V5">
-        <v>0.01769230769230769</v>
+        <v>0.1172360248447205</v>
       </c>
       <c r="W5">
-        <v>0.1465306122448979</v>
+        <v>0.1054874800213106</v>
       </c>
       <c r="X5">
-        <v>0.07162369163031648</v>
+        <v>0.05236286568940925</v>
       </c>
       <c r="Y5">
-        <v>0.07490692061458146</v>
+        <v>0.05312461433190137</v>
       </c>
       <c r="Z5">
-        <v>0.1341724056043695</v>
+        <v>0.6953196912837215</v>
       </c>
       <c r="AA5">
-        <v>0.0738858545080345</v>
+        <v>0.1426885303454253</v>
       </c>
       <c r="AB5">
-        <v>0.05125154303230905</v>
+        <v>0.05231019550110907</v>
       </c>
       <c r="AC5">
-        <v>0.02263431147572546</v>
+        <v>0.09037833484431618</v>
       </c>
       <c r="AD5">
-        <v>194.1</v>
+        <v>3.75</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>194.1</v>
+        <v>3.75</v>
       </c>
       <c r="AG5">
-        <v>192.72</v>
+        <v>-56.65</v>
       </c>
       <c r="AH5">
-        <v>0.713340683572216</v>
+        <v>0.007226129684940745</v>
       </c>
       <c r="AI5">
-        <v>0.78582995951417</v>
+        <v>0.02270663033605813</v>
       </c>
       <c r="AJ5">
-        <v>0.7118794326241134</v>
+        <v>-0.1235415985170646</v>
       </c>
       <c r="AK5">
-        <v>0.7846266590668513</v>
+        <v>-0.5408114558472553</v>
       </c>
       <c r="AL5">
-        <v>5.91</v>
+        <v>0.089</v>
       </c>
       <c r="AM5">
-        <v>5.91</v>
+        <v>-2.541</v>
       </c>
       <c r="AN5">
-        <v>10.78333333333333</v>
+        <v>0.1175548589341693</v>
       </c>
       <c r="AO5">
-        <v>2.859560067681895</v>
+        <v>300</v>
       </c>
       <c r="AP5">
-        <v>10.70666666666667</v>
+        <v>-1.775862068965517</v>
       </c>
       <c r="AQ5">
-        <v>2.859560067681895</v>
+        <v>-10.50767414403778</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Group Psagot for Finance and Investments Ltd (TASE:GPST)</t>
+          <t>Michlol Finance Ltd (TASE:MCLL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1102,26 +1117,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1.257</v>
-      </c>
       <c r="G6">
-        <v>0.07776699029126213</v>
+        <v>0.4817351598173517</v>
       </c>
       <c r="H6">
-        <v>0.07776699029126213</v>
+        <v>0.4817351598173517</v>
       </c>
       <c r="I6">
-        <v>0.1378640776699029</v>
+        <v>0.7374429223744292</v>
       </c>
       <c r="J6">
-        <v>0.1378640776699029</v>
+        <v>0.5610028750211399</v>
       </c>
       <c r="K6">
-        <v>2.99</v>
+        <v>10.3</v>
       </c>
       <c r="L6">
-        <v>0.02902912621359224</v>
+        <v>0.2351598173515982</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1145,73 +1157,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>16.8</v>
+        <v>9.73</v>
       </c>
       <c r="V6">
-        <v>0.2688</v>
+        <v>0.1579545454545455</v>
       </c>
       <c r="W6">
-        <v>0.06028225806451613</v>
+        <v>0.1947069943289225</v>
       </c>
       <c r="X6">
-        <v>0.08545930516269003</v>
+        <v>0.1054945731247002</v>
       </c>
       <c r="Y6">
-        <v>-0.02517704709817389</v>
+        <v>0.08921242120422231</v>
       </c>
       <c r="Z6">
-        <v>0.5573593073593073</v>
+        <v>0.1783242406970116</v>
       </c>
       <c r="AA6">
-        <v>0.07683982683982683</v>
+        <v>0.1000404117169853</v>
       </c>
       <c r="AB6">
-        <v>0.05616535244949007</v>
+        <v>0.05494121020848548</v>
       </c>
       <c r="AC6">
-        <v>0.02067447439033676</v>
+        <v>0.04509920150849979</v>
       </c>
       <c r="AD6">
-        <v>255.3</v>
+        <v>315.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>255.3</v>
+        <v>315.6</v>
       </c>
       <c r="AG6">
-        <v>238.5</v>
+        <v>305.87</v>
       </c>
       <c r="AH6">
-        <v>0.8033354310887351</v>
+        <v>0.8366914103923647</v>
       </c>
       <c r="AI6">
-        <v>0.7968164794007492</v>
+        <v>0.8292170257488176</v>
       </c>
       <c r="AJ6">
-        <v>0.792358803986711</v>
+        <v>0.8323672680763055</v>
       </c>
       <c r="AK6">
-        <v>0.7855731225296442</v>
+        <v>0.8247364305551811</v>
       </c>
       <c r="AL6">
-        <v>8.16</v>
+        <v>19.2</v>
       </c>
       <c r="AM6">
-        <v>8.16</v>
+        <v>19.2</v>
       </c>
       <c r="AN6">
-        <v>9.744274809160306</v>
+        <v>9.392857142857142</v>
       </c>
       <c r="AO6">
-        <v>1.740196078431372</v>
+        <v>1.682291666666667</v>
       </c>
       <c r="AP6">
-        <v>9.103053435114504</v>
+        <v>9.103273809523809</v>
       </c>
       <c r="AQ6">
-        <v>1.740196078431372</v>
+        <v>1.682291666666667</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Isracard Ltd. (TASE:ISCD)</t>
+          <t>Group Psagot for Finance and Investments Ltd (TASE:GPST)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1231,109 +1243,115 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.076</v>
-      </c>
-      <c r="E7">
-        <v>-0.0599</v>
+        <v>1.152</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.2545598194130925</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.2471783295711061</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.1309255079006772</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.1309255079006772</v>
       </c>
       <c r="K7">
-        <v>55.9</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L7">
-        <v>0.08206106870229007</v>
+        <v>-0.1103837471783296</v>
       </c>
       <c r="M7">
-        <v>41.8</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.07200689061154177</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.7477638640429338</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>41.8</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.07200689061154177</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.7477638640429338</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>1043.1</v>
+        <v>15</v>
       </c>
       <c r="V7">
-        <v>1.796899224806201</v>
+        <v>0.3440366972477064</v>
       </c>
       <c r="W7">
-        <v>0.06622438099751214</v>
+        <v>-0.1781420765027322</v>
       </c>
       <c r="X7">
-        <v>0.0539468248809558</v>
+        <v>0.08487203524503648</v>
       </c>
       <c r="Y7">
-        <v>0.01227755611655634</v>
+        <v>-0.2630141117477687</v>
       </c>
       <c r="Z7">
-        <v>31.83177570093478</v>
+        <v>0.3087108013937282</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.04041811846689895</v>
       </c>
       <c r="AB7">
-        <v>0.05057525210356946</v>
+        <v>0.05469260442299605</v>
       </c>
       <c r="AC7">
-        <v>-0.05057525210356946</v>
+        <v>-0.01427448595609709</v>
       </c>
       <c r="AD7">
-        <v>260.6</v>
+        <v>136.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>260.6</v>
+        <v>136.8</v>
       </c>
       <c r="AG7">
-        <v>-782.4999999999999</v>
+        <v>121.8</v>
       </c>
       <c r="AH7">
-        <v>0.3098323623825943</v>
+        <v>0.7583148558758315</v>
       </c>
       <c r="AI7">
-        <v>0.2494257274119449</v>
+        <v>0.7315508021390374</v>
       </c>
       <c r="AJ7">
-        <v>3.873762376237625</v>
+        <v>0.7363966142684402</v>
       </c>
       <c r="AK7">
-        <v>-460.2941176470156</v>
+        <v>0.7081395348837209</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>7.7</v>
+      </c>
+      <c r="AN7">
+        <v>5.796610169491526</v>
+      </c>
+      <c r="AO7">
+        <v>1.506493506493506</v>
+      </c>
+      <c r="AP7">
+        <v>5.161016949152542</v>
+      </c>
+      <c r="AQ7">
+        <v>1.506493506493506</v>
       </c>
     </row>
     <row r="8">
@@ -1344,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Opal Balance Investments Ltd (TASE:OPAL)</t>
+          <t>Nawi Brothers Group Ltd (TASE:NAWI)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,10 +1371,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.16</v>
+        <v>0.127</v>
       </c>
       <c r="E8">
-        <v>0.162</v>
+        <v>0.146</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1371,28 +1389,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>8.15</v>
+        <v>37.4</v>
       </c>
       <c r="L8">
-        <v>0.4335106382978723</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="M8">
-        <v>4.37</v>
+        <v>15.8</v>
       </c>
       <c r="N8">
-        <v>0.07761989342806395</v>
+        <v>0.07101123595505618</v>
       </c>
       <c r="O8">
-        <v>0.5361963190184049</v>
+        <v>0.4224598930481284</v>
       </c>
       <c r="P8">
-        <v>4.37</v>
+        <v>15.8</v>
       </c>
       <c r="Q8">
-        <v>0.07761989342806395</v>
+        <v>0.07101123595505618</v>
       </c>
       <c r="R8">
-        <v>0.5361963190184049</v>
+        <v>0.4224598930481284</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1401,55 +1419,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>6.35</v>
+        <v>0.855</v>
       </c>
       <c r="V8">
-        <v>0.1127886323268206</v>
+        <v>0.003842696629213483</v>
       </c>
       <c r="W8">
-        <v>0.1484517304189436</v>
+        <v>0.1967385586533403</v>
       </c>
       <c r="X8">
-        <v>0.0655120234897387</v>
+        <v>0.08884785135297313</v>
       </c>
       <c r="Y8">
-        <v>0.08293970692920485</v>
+        <v>0.1078907073003672</v>
       </c>
       <c r="Z8">
-        <v>0.1572037795802325</v>
+        <v>0.05605845367851751</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05112981997678492</v>
+        <v>0.05127228725414276</v>
       </c>
       <c r="AC8">
-        <v>-0.05112981997678492</v>
+        <v>-0.05127228725414276</v>
       </c>
       <c r="AD8">
-        <v>100.4</v>
+        <v>783.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>100.4</v>
+        <v>783.3</v>
       </c>
       <c r="AG8">
-        <v>94.05000000000001</v>
+        <v>782.4449999999999</v>
       </c>
       <c r="AH8">
-        <v>0.6407147415443524</v>
+        <v>0.7787830582620799</v>
       </c>
       <c r="AI8">
-        <v>0.6519480519480519</v>
+        <v>0.7890601390148081</v>
       </c>
       <c r="AJ8">
-        <v>0.6255404057199867</v>
+        <v>0.7785948484742946</v>
       </c>
       <c r="AK8">
-        <v>0.6369793430409754</v>
+        <v>0.7888783025573552</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1466,7 +1484,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Peninsula Group Ltd (TASE:PEN)</t>
+          <t>Menif - Financial Services Ltd (TASE:MNIF)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1474,12 +1492,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.197</v>
-      </c>
-      <c r="E9">
-        <v>0.206</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1493,28 +1505,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="L9">
-        <v>0.4676258992805755</v>
+        <v>0.6724511930585683</v>
       </c>
       <c r="M9">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="N9">
-        <v>0.08054226475279107</v>
+        <v>0.06612601372426699</v>
       </c>
       <c r="O9">
-        <v>0.7769230769230769</v>
+        <v>0.3419354838709677</v>
       </c>
       <c r="P9">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="Q9">
-        <v>0.08054226475279107</v>
+        <v>0.06612601372426699</v>
       </c>
       <c r="R9">
-        <v>0.7769230769230769</v>
+        <v>0.3419354838709677</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1523,55 +1535,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>14.2</v>
+        <v>6.64</v>
       </c>
       <c r="V9">
-        <v>0.113237639553429</v>
+        <v>0.04142233312538989</v>
       </c>
       <c r="W9">
-        <v>0.08338678640153944</v>
+        <v>0.3287380699893955</v>
       </c>
       <c r="X9">
-        <v>0.06773572802525016</v>
+        <v>0.08548363919407136</v>
       </c>
       <c r="Y9">
-        <v>0.01565105837628929</v>
+        <v>0.2432544307953242</v>
       </c>
       <c r="Z9">
-        <v>0.08870453095086153</v>
+        <v>0.09849375066766371</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05118064396560197</v>
+        <v>0.05129454304751642</v>
       </c>
       <c r="AC9">
-        <v>-0.05118064396560197</v>
+        <v>-0.05129454304751642</v>
       </c>
       <c r="AD9">
-        <v>255.8</v>
+        <v>512.4</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>255.8</v>
+        <v>512.4</v>
       </c>
       <c r="AG9">
-        <v>241.6</v>
+        <v>505.76</v>
       </c>
       <c r="AH9">
-        <v>0.6710388247639034</v>
+        <v>0.7617065556711757</v>
       </c>
       <c r="AI9">
-        <v>0.6393401649587603</v>
+        <v>0.8241917323467911</v>
       </c>
       <c r="AJ9">
-        <v>0.6583106267029973</v>
+        <v>0.7593309912019939</v>
       </c>
       <c r="AK9">
-        <v>0.626068929774553</v>
+        <v>0.8222937599583781</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S.R. Accord Ltd. (TASE:SRAC)</t>
+          <t>Gamla Harel Residential Real Estate Ltd (TASE:GMLA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1596,12 +1608,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.273</v>
-      </c>
-      <c r="E10">
-        <v>0.254</v>
-      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1615,85 +1621,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>23.4</v>
+        <v>11.7</v>
       </c>
       <c r="L10">
-        <v>0.6358695652173914</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="M10">
-        <v>7.914</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.05394683026584867</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.3382051282051282</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>7.3</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04976141785957737</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.311965811965812</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>0.6139999999999999</v>
-      </c>
-      <c r="T10">
-        <v>0.0775840283042709</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.74</v>
+        <v>0.123</v>
       </c>
       <c r="V10">
-        <v>0.03231083844580777</v>
+        <v>0.001587096774193548</v>
       </c>
       <c r="W10">
-        <v>0.2802395209580838</v>
+        <v>0.1638655462184874</v>
       </c>
       <c r="X10">
-        <v>0.07013148011843401</v>
+        <v>0.08467570299573789</v>
       </c>
       <c r="Y10">
-        <v>0.2101080408396498</v>
+        <v>0.07918984322274948</v>
       </c>
       <c r="Z10">
-        <v>0.1192868719611021</v>
+        <v>0.0650732901717273</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05122659988002292</v>
+        <v>0.05130040925212498</v>
       </c>
       <c r="AC10">
-        <v>-0.05122659988002292</v>
+        <v>-0.05130040925212498</v>
       </c>
       <c r="AD10">
-        <v>339.8</v>
+        <v>241.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>339.8</v>
+        <v>241.7</v>
       </c>
       <c r="AG10">
-        <v>335.06</v>
+        <v>241.577</v>
       </c>
       <c r="AH10">
-        <v>0.6984583761562179</v>
+        <v>0.7572055137844611</v>
       </c>
       <c r="AI10">
-        <v>0.7874855156431054</v>
+        <v>0.754840724547158</v>
       </c>
       <c r="AJ10">
-        <v>0.6954915310528064</v>
+        <v>0.7571119196933656</v>
       </c>
       <c r="AK10">
-        <v>0.785125128878058</v>
+        <v>0.7547465141200399</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1710,7 +1713,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Menif - Financial Services Ltd (TASE:MNIF)</t>
+          <t>Michman Basad Ltd (TASE:MCMN)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1731,85 +1734,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>22.7</v>
+        <v>12</v>
       </c>
       <c r="L11">
-        <v>0.6735905044510385</v>
+        <v>0.48</v>
       </c>
       <c r="M11">
-        <v>12.3</v>
+        <v>2.504</v>
       </c>
       <c r="N11">
-        <v>0.07899807321772641</v>
+        <v>0.03771084337349397</v>
       </c>
       <c r="O11">
-        <v>0.5418502202643173</v>
+        <v>0.2086666666666667</v>
       </c>
       <c r="P11">
-        <v>12.3</v>
+        <v>1.7</v>
       </c>
       <c r="Q11">
-        <v>0.07899807321772641</v>
+        <v>0.02560240963855421</v>
       </c>
       <c r="R11">
-        <v>0.5418502202643173</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.804</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.3210862619808307</v>
       </c>
       <c r="U11">
-        <v>5.65</v>
+        <v>5.28</v>
       </c>
       <c r="V11">
-        <v>0.03628773281952473</v>
+        <v>0.07951807228915662</v>
       </c>
       <c r="W11">
-        <v>0.2489035087719298</v>
+        <v>0.4395604395604396</v>
       </c>
       <c r="X11">
-        <v>0.07117539299035051</v>
+        <v>0.07663932088158684</v>
       </c>
       <c r="Y11">
-        <v>0.1777281157815793</v>
+        <v>0.3629211186788527</v>
       </c>
       <c r="Z11">
-        <v>0.1166089965397924</v>
+        <v>0.1330211769713738</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.0512443120921775</v>
+        <v>0.05137361549946642</v>
       </c>
       <c r="AC11">
-        <v>-0.0512443120921775</v>
+        <v>-0.05137361549946642</v>
       </c>
       <c r="AD11">
-        <v>379.4</v>
+        <v>155.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>379.4</v>
+        <v>155.7</v>
       </c>
       <c r="AG11">
-        <v>373.75</v>
+        <v>150.42</v>
       </c>
       <c r="AH11">
-        <v>0.7090263502149132</v>
+        <v>0.7010355695632597</v>
       </c>
       <c r="AI11">
-        <v>0.8005908419497785</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="AJ11">
-        <v>0.7059212390216262</v>
+        <v>0.6937551886357347</v>
       </c>
       <c r="AK11">
-        <v>0.798184730379071</v>
+        <v>0.8129931899254135</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1826,7 +1829,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Direct Finance of Direct Group (2006) Ltd (TASE:DIFI)</t>
+          <t>Isracard Ltd. (TASE:ISCD)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1834,6 +1837,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.0709</v>
+      </c>
+      <c r="E12">
+        <v>-0.0447</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1847,28 +1856,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>66.5</v>
+        <v>56.1</v>
       </c>
       <c r="L12">
-        <v>0.3674033149171271</v>
+        <v>0.07325672499347088</v>
       </c>
       <c r="M12">
-        <v>33.9</v>
+        <v>17.8</v>
       </c>
       <c r="N12">
-        <v>0.07208165001063151</v>
+        <v>0.02344264454102463</v>
       </c>
       <c r="O12">
-        <v>0.5097744360902255</v>
+        <v>0.3172905525846703</v>
       </c>
       <c r="P12">
-        <v>33.9</v>
+        <v>17.8</v>
       </c>
       <c r="Q12">
-        <v>0.07208165001063151</v>
+        <v>0.02344264454102463</v>
       </c>
       <c r="R12">
-        <v>0.5097744360902255</v>
+        <v>0.3172905525846703</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1877,55 +1886,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>8.140000000000001</v>
+        <v>228.6</v>
       </c>
       <c r="V12">
-        <v>0.01730810121199235</v>
+        <v>0.3010667720268669</v>
       </c>
       <c r="W12">
-        <v>0.274793388429752</v>
+        <v>0.07153787299158378</v>
       </c>
       <c r="X12">
-        <v>0.07219455391486097</v>
+        <v>0.05891394409926315</v>
       </c>
       <c r="Y12">
-        <v>0.2025988345148911</v>
+        <v>0.01262392889232063</v>
       </c>
       <c r="Z12">
-        <v>0.166651321241138</v>
+        <v>450.4705882352218</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.05126044626348948</v>
+        <v>0.05352284731313342</v>
       </c>
       <c r="AC12">
-        <v>-0.05126044626348948</v>
+        <v>-0.05352284731313342</v>
       </c>
       <c r="AD12">
-        <v>1201.3</v>
+        <v>484.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1201.3</v>
+        <v>484.5</v>
       </c>
       <c r="AG12">
-        <v>1193.16</v>
+        <v>255.9</v>
       </c>
       <c r="AH12">
-        <v>0.7186527877482651</v>
+        <v>0.3895320791123975</v>
       </c>
       <c r="AI12">
-        <v>0.7861910994764397</v>
+        <v>0.3849209501867005</v>
       </c>
       <c r="AJ12">
-        <v>0.7172760390992269</v>
+        <v>0.2520685579196218</v>
       </c>
       <c r="AK12">
-        <v>0.7850459910781256</v>
+        <v>0.248422483254053</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1942,7 +1951,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gamla - Harel Residential Real-Estate Ltd (TASE:GMLA)</t>
+          <t>Opal Balance Investments Ltd (TASE:OPAL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1950,6 +1959,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="E13">
+        <v>0.05019999999999999</v>
+      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -1963,28 +1978,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>7.97</v>
+        <v>7.31</v>
       </c>
       <c r="L13">
-        <v>0.6083969465648855</v>
+        <v>0.415340909090909</v>
       </c>
       <c r="M13">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="N13">
-        <v>0.0461890243902439</v>
+        <v>0.08023529411764706</v>
       </c>
       <c r="O13">
-        <v>0.3801756587202008</v>
+        <v>0.466484268125855</v>
       </c>
       <c r="P13">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="Q13">
-        <v>0.0461890243902439</v>
+        <v>0.08023529411764706</v>
       </c>
       <c r="R13">
-        <v>0.3801756587202008</v>
+        <v>0.466484268125855</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1993,55 +2008,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.099</v>
+        <v>3.41</v>
       </c>
       <c r="V13">
-        <v>0.001509146341463415</v>
+        <v>0.08023529411764706</v>
       </c>
       <c r="W13">
-        <v>0.1308702791461412</v>
+        <v>0.1363805970149254</v>
       </c>
       <c r="X13">
-        <v>0.07657251216451358</v>
+        <v>0.0694900554463499</v>
       </c>
       <c r="Y13">
-        <v>0.05429776698162764</v>
+        <v>0.06689054156857546</v>
       </c>
       <c r="Z13">
-        <v>0.09214774589731504</v>
+        <v>0.1192008127328141</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05131912145649137</v>
+        <v>0.05426517214240925</v>
       </c>
       <c r="AC13">
-        <v>-0.05131912145649137</v>
+        <v>-0.05426517214240925</v>
       </c>
       <c r="AD13">
-        <v>200.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>200.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AG13">
-        <v>200.601</v>
+        <v>66.99000000000001</v>
       </c>
       <c r="AH13">
-        <v>0.7536612842658656</v>
+        <v>0.6235606731620904</v>
       </c>
       <c r="AI13">
-        <v>0.7375964718853362</v>
+        <v>0.5663716814159292</v>
       </c>
       <c r="AJ13">
-        <v>0.7535696710380502</v>
+        <v>0.6118366974152891</v>
       </c>
       <c r="AK13">
-        <v>0.7375009650699814</v>
+        <v>0.554140127388535</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2058,7 +2073,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nawi Brothers Group Ltd (TASE:NAWI)</t>
+          <t>Erech Finance Cahalacha Ltd (TASE:EFNC)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2066,104 +2081,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.158</v>
-      </c>
-      <c r="E14">
-        <v>0.182</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="K14">
-        <v>39.3</v>
-      </c>
-      <c r="L14">
-        <v>0.6943462897526501</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="M14">
-        <v>21.5</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.09388646288209607</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.5470737913486006</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>21.5</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.09388646288209607</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.5470737913486006</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>0.526</v>
+        <v>0.236</v>
       </c>
       <c r="V14">
-        <v>0.002296943231441048</v>
+        <v>0.07195121951219512</v>
       </c>
       <c r="W14">
-        <v>0.2024729520865533</v>
+        <v>-0.5561290322580644</v>
       </c>
       <c r="X14">
-        <v>0.0785286890331332</v>
+        <v>0.07274105560469435</v>
       </c>
       <c r="Y14">
-        <v>0.1239442630534201</v>
+        <v>-0.6288700878627588</v>
       </c>
       <c r="Z14">
-        <v>0.06155586248898846</v>
+        <v>0</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05134086759238156</v>
+        <v>0.05439104642335339</v>
       </c>
       <c r="AC14">
-        <v>-0.05134086759238156</v>
+        <v>-0.05439104642335339</v>
       </c>
       <c r="AD14">
-        <v>752.3</v>
+        <v>6.46</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>752.3</v>
+        <v>6.46</v>
       </c>
       <c r="AG14">
-        <v>751.774</v>
+        <v>6.224</v>
       </c>
       <c r="AH14">
-        <v>0.7666360949760521</v>
+        <v>0.6632443531827515</v>
       </c>
       <c r="AI14">
-        <v>0.7982809847198642</v>
+        <v>0.5218093699515348</v>
       </c>
       <c r="AJ14">
-        <v>0.7665109393193539</v>
+        <v>0.654882154882155</v>
       </c>
       <c r="AK14">
-        <v>0.79816833249458</v>
+        <v>0.5125164690382081</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2180,7 +2171,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Michman Besd Ltd (TASE:MCMN)</t>
+          <t>S.R. Accord Ltd. (TASE:SRAC)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2188,6 +2179,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D15">
+        <v>0.169</v>
+      </c>
+      <c r="E15">
+        <v>0.181</v>
+      </c>
       <c r="G15">
         <v>0</v>
       </c>
@@ -2201,82 +2198,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>3.06</v>
+        <v>17.3</v>
       </c>
       <c r="L15">
-        <v>0.1738636363636364</v>
+        <v>0.6245487364620939</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>7.97</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.08241985522233712</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.4606936416184971</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>4.72</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.04881075491209927</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.2728323699421965</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.25</v>
+      </c>
+      <c r="T15">
+        <v>0.4077791718946048</v>
       </c>
       <c r="U15">
-        <v>5.76</v>
+        <v>3.12</v>
       </c>
       <c r="V15">
-        <v>0.07944827586206896</v>
+        <v>0.03226473629782833</v>
       </c>
       <c r="W15">
-        <v>0.1577319587628866</v>
+        <v>0.1957013574660633</v>
       </c>
       <c r="X15">
-        <v>0.06994843685612159</v>
+        <v>0.07714946846229298</v>
       </c>
       <c r="Y15">
-        <v>0.08778352190676503</v>
+        <v>0.1185518890037704</v>
       </c>
       <c r="Z15">
-        <v>0.1990274793622074</v>
+        <v>0.06820812095245131</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.05535306186441299</v>
+        <v>0.05452464295446173</v>
       </c>
       <c r="AC15">
-        <v>-0.05535306186441299</v>
+        <v>-0.05452464295446173</v>
       </c>
       <c r="AD15">
-        <v>166.4</v>
+        <v>231.5</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>166.4</v>
+        <v>231.5</v>
       </c>
       <c r="AG15">
-        <v>160.64</v>
+        <v>228.38</v>
       </c>
       <c r="AH15">
-        <v>0.6965257429886982</v>
+        <v>0.7053625837903718</v>
       </c>
       <c r="AI15">
-        <v>0.8590604026845637</v>
+        <v>0.7070861331704338</v>
       </c>
       <c r="AJ15">
-        <v>0.6890280518143604</v>
+        <v>0.7025347606742955</v>
       </c>
       <c r="AK15">
-        <v>0.8547408747472597</v>
+        <v>0.7042679166152708</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blender Financial Technologies (TASE:BLND)</t>
+          <t>Peninsula Group Ltd (TASE:PEN)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2301,6 +2301,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.193</v>
+      </c>
+      <c r="E16">
+        <v>0.214</v>
+      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2314,82 +2320,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>-6.96</v>
+        <v>14.8</v>
       </c>
       <c r="L16">
-        <v>-1.669064748201439</v>
+        <v>0.5</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>15.64</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.1674518201284796</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.056756756756757</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>11.7</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.1252676659528908</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>0.7905405405405405</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.94</v>
+      </c>
+      <c r="T16">
+        <v>0.2519181585677749</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="V16">
-        <v>0.9513742071881606</v>
+        <v>0.310492505353319</v>
       </c>
       <c r="W16">
-        <v>-0.2817813765182186</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="X16">
-        <v>0.07231921560583626</v>
+        <v>0.08095220977332833</v>
       </c>
       <c r="Y16">
-        <v>-0.3541005921240549</v>
+        <v>0.02161189279077423</v>
       </c>
       <c r="Z16">
-        <v>0.2482142857142857</v>
+        <v>0.07670380927701477</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.05552996230265501</v>
+        <v>0.05461565255037797</v>
       </c>
       <c r="AC16">
-        <v>-0.05552996230265501</v>
+        <v>-0.05461565255037797</v>
       </c>
       <c r="AD16">
-        <v>24.3</v>
+        <v>257.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>24.3</v>
+        <v>257.8</v>
       </c>
       <c r="AG16">
-        <v>15.3</v>
+        <v>228.8</v>
       </c>
       <c r="AH16">
-        <v>0.7197867298578198</v>
+        <v>0.7340546697038723</v>
       </c>
       <c r="AI16">
-        <v>0.6014851485148515</v>
+        <v>0.6574853353736292</v>
       </c>
       <c r="AJ16">
-        <v>0.6179321486268174</v>
+        <v>0.7101179391682184</v>
       </c>
       <c r="AK16">
-        <v>0.4872611464968153</v>
+        <v>0.6301294409253649</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2406,7 +2415,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M.L.R.N Projects and Trade Ltd. (TASE:MLRN)</t>
+          <t>Blender Financial Technologies (TASE:BLND)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2427,85 +2436,82 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>11.8</v>
+        <v>-3.39</v>
       </c>
       <c r="L17">
-        <v>0.4169611307420495</v>
+        <v>-0.4562584118438762</v>
       </c>
       <c r="M17">
-        <v>4.07</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.07400000000000001</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.3449152542372881</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4.07</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.07400000000000001</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.3449152542372881</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>1.78</v>
+        <v>12.9</v>
       </c>
       <c r="V17">
-        <v>0.03236363636363637</v>
+        <v>1.121739130434783</v>
       </c>
       <c r="W17">
-        <v>0.3113456464379947</v>
+        <v>-0.2105590062111801</v>
       </c>
       <c r="X17">
-        <v>0.09053916702470005</v>
+        <v>0.0814561448827269</v>
       </c>
       <c r="Y17">
-        <v>0.2208064794132947</v>
+        <v>-0.292015151093907</v>
       </c>
       <c r="Z17">
-        <v>0.1544759825327511</v>
+        <v>0.236624203821656</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.05631993222401549</v>
+        <v>0.0546263998870247</v>
       </c>
       <c r="AC17">
-        <v>-0.05631993222401549</v>
+        <v>-0.0546263998870247</v>
       </c>
       <c r="AD17">
-        <v>256.9</v>
+        <v>32.3</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>256.9</v>
+        <v>32.3</v>
       </c>
       <c r="AG17">
-        <v>255.12</v>
+        <v>19.4</v>
       </c>
       <c r="AH17">
-        <v>0.8236614299454953</v>
+        <v>0.7374429223744292</v>
       </c>
       <c r="AI17">
-        <v>0.7703148425787105</v>
+        <v>0.6757322175732218</v>
       </c>
       <c r="AJ17">
-        <v>0.8226492970463045</v>
+        <v>0.627831715210356</v>
       </c>
       <c r="AK17">
-        <v>0.7690823586157</v>
+        <v>0.5558739255014327</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2522,7 +2528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Erech Finance Cahalacha Ltd (TASE:EFNC)</t>
+          <t>M.L.R.N Projects and Trade Ltd. (TASE:MLRN)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2531,7 +2537,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>-0.002325581395348838</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2543,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>-1.39</v>
+        <v>10.9</v>
       </c>
       <c r="L18">
-        <v>-0.4617940199335548</v>
+        <v>0.4430894308943089</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2555,7 +2561,7 @@
         <v>-0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P18">
         <v>-0</v>
@@ -2564,67 +2570,424 @@
         <v>-0</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="U18">
-        <v>0.8110000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="V18">
-        <v>0.1830699774266366</v>
+        <v>0.02633744855967078</v>
       </c>
       <c r="W18">
-        <v>-0.09928571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="X18">
-        <v>0.09094586052601639</v>
+        <v>0.09032360927541158</v>
       </c>
       <c r="Y18">
-        <v>-0.1902315748117307</v>
+        <v>0.07634305739125508</v>
       </c>
       <c r="Z18">
-        <v>0.1454106280193236</v>
+        <v>0.07675028079371023</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.05633093774006873</v>
+        <v>0.05477891387732137</v>
       </c>
       <c r="AC18">
-        <v>-0.05633093774006873</v>
+        <v>-0.05477891387732137</v>
       </c>
       <c r="AD18">
-        <v>20.9</v>
+        <v>178</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>20.9</v>
+        <v>178</v>
       </c>
       <c r="AG18">
-        <v>20.089</v>
+        <v>176.72</v>
       </c>
       <c r="AH18">
-        <v>0.8251085669166995</v>
+        <v>0.7855251544571933</v>
       </c>
       <c r="AI18">
-        <v>0.5757575757575758</v>
+        <v>0.7189014539579968</v>
       </c>
       <c r="AJ18">
-        <v>0.8193237897140992</v>
+        <v>0.7843067637138292</v>
       </c>
       <c r="AK18">
-        <v>0.5660627236608526</v>
+        <v>0.7174407275089315</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
         <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Direct Finance of Direct Group (2006)Ltd (TASE:DIFI)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>44.6</v>
+      </c>
+      <c r="L19">
+        <v>0.1836902800658979</v>
+      </c>
+      <c r="M19">
+        <v>23.7</v>
+      </c>
+      <c r="N19">
+        <v>0.06653565412689501</v>
+      </c>
+      <c r="O19">
+        <v>0.531390134529148</v>
+      </c>
+      <c r="P19">
+        <v>23.7</v>
+      </c>
+      <c r="Q19">
+        <v>0.06653565412689501</v>
+      </c>
+      <c r="R19">
+        <v>0.531390134529148</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>4.2</v>
+      </c>
+      <c r="V19">
+        <v>0.01179112857944975</v>
+      </c>
+      <c r="W19">
+        <v>0.1365166819712274</v>
+      </c>
+      <c r="X19">
+        <v>0.09933847662335774</v>
+      </c>
+      <c r="Y19">
+        <v>0.0371782053478697</v>
+      </c>
+      <c r="Z19">
+        <v>0.1597515560643744</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05488568984851713</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05488568984851713</v>
+      </c>
+      <c r="AD19">
+        <v>1613.8</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>1613.8</v>
+      </c>
+      <c r="AG19">
+        <v>1609.6</v>
+      </c>
+      <c r="AH19">
+        <v>0.8191878172588832</v>
+      </c>
+      <c r="AI19">
+        <v>0.8273775954883363</v>
+      </c>
+      <c r="AJ19">
+        <v>0.8188015057482958</v>
+      </c>
+      <c r="AK19">
+        <v>0.827005086574526</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Guideline Group Information Technologies Ltd (TASE:GUID)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-0.0177</v>
+      </c>
+      <c r="G20">
+        <v>0.1039393939393939</v>
+      </c>
+      <c r="H20">
+        <v>0.102020202020202</v>
+      </c>
+      <c r="I20">
+        <v>-0.0153030303030303</v>
+      </c>
+      <c r="J20">
+        <v>-0.0153030303030303</v>
+      </c>
+      <c r="K20">
+        <v>-0.346</v>
+      </c>
+      <c r="L20">
+        <v>-0.01747474747474747</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>3.26</v>
+      </c>
+      <c r="V20">
+        <v>0.194047619047619</v>
+      </c>
+      <c r="W20">
+        <v>-0.01119741100323625</v>
+      </c>
+      <c r="X20">
+        <v>0.05234414598747072</v>
+      </c>
+      <c r="Y20">
+        <v>-0.06354155699070696</v>
+      </c>
+      <c r="Z20">
+        <v>1.331002957784351</v>
+      </c>
+      <c r="AA20">
+        <v>-0.02036837859639688</v>
+      </c>
+      <c r="AB20">
+        <v>0.05230455019347084</v>
+      </c>
+      <c r="AC20">
+        <v>-0.07267292878986772</v>
+      </c>
+      <c r="AD20">
+        <v>0.092</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0.092</v>
+      </c>
+      <c r="AG20">
+        <v>-3.168</v>
+      </c>
+      <c r="AH20">
+        <v>0.005446365143263084</v>
+      </c>
+      <c r="AI20">
+        <v>0.003263337116912599</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.232394366197183</v>
+      </c>
+      <c r="AK20">
+        <v>-0.1270656184822718</v>
+      </c>
+      <c r="AL20">
+        <v>0.061</v>
+      </c>
+      <c r="AM20">
+        <v>-0.204</v>
+      </c>
+      <c r="AN20">
+        <v>0.6618705035971222</v>
+      </c>
+      <c r="AO20">
+        <v>-4.967213114754099</v>
+      </c>
+      <c r="AP20">
+        <v>-22.79136690647482</v>
+      </c>
+      <c r="AQ20">
+        <v>1.485294117647059</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The INX Digital Company, Inc. (NEOE:INXD)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>-1.387692307692308</v>
+      </c>
+      <c r="H21">
+        <v>-1.730769230769231</v>
+      </c>
+      <c r="I21">
+        <v>-1.346153846153846</v>
+      </c>
+      <c r="J21">
+        <v>-1.211538461538462</v>
+      </c>
+      <c r="K21">
+        <v>1.28</v>
+      </c>
+      <c r="L21">
+        <v>0.09846153846153846</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>-0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>12.8</v>
+      </c>
+      <c r="V21">
+        <v>0.2195540308747856</v>
+      </c>
+      <c r="W21">
+        <v>-0.08590604026845637</v>
+      </c>
+      <c r="X21">
+        <v>0.05245863937711538</v>
+      </c>
+      <c r="Y21">
+        <v>-0.1383646796455718</v>
+      </c>
+      <c r="AB21">
+        <v>0.05237212568113718</v>
+      </c>
+      <c r="AD21">
+        <v>0.962</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0.962</v>
+      </c>
+      <c r="AG21">
+        <v>-11.838</v>
+      </c>
+      <c r="AH21">
+        <v>0.0162329992237859</v>
+      </c>
+      <c r="AI21">
+        <v>-0.1355311355311355</v>
+      </c>
+      <c r="AJ21">
+        <v>-0.2547888597133142</v>
+      </c>
+      <c r="AK21">
+        <v>0.5949341642376118</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-0.754</v>
+      </c>
+      <c r="AN21">
+        <v>-0.05435028248587571</v>
+      </c>
+      <c r="AP21">
+        <v>0.668813559322034</v>
+      </c>
+      <c r="AQ21">
+        <v>23.20954907161804</v>
       </c>
     </row>
   </sheetData>
